--- a/RPRX.xlsx
+++ b/RPRX.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shkre\code\models\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CB7C7F0-6DEA-488A-8E71-DF0913C347F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93981357-2752-4B35-B938-7439E862438B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-26700" yWindow="540" windowWidth="26490" windowHeight="19650" activeTab="1" xr2:uid="{94D9BD71-8B15-4AF3-9192-B3E60893D3C5}"/>
+    <workbookView xWindow="17400" yWindow="1910" windowWidth="19160" windowHeight="9340" xr2:uid="{94D9BD71-8B15-4AF3-9192-B3E60893D3C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="133">
   <si>
     <t>Price</t>
   </si>
@@ -433,6 +433,9 @@
   </si>
   <si>
     <t>Q424</t>
+  </si>
+  <si>
+    <t>Q126</t>
   </si>
 </sst>
 </file>
@@ -1029,14 +1032,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B84BD893-C181-4171-97CF-57470801B437}">
   <dimension ref="B2:M17"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.26953125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:13" ht="13" x14ac:dyDescent="0.3">
       <c r="B2" s="13" t="s">
         <v>75</v>
       </c>
@@ -1057,10 +1060,10 @@
         <v>0</v>
       </c>
       <c r="L2" s="1">
-        <v>29.37</v>
-      </c>
-    </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B3" s="8" t="s">
         <v>63</v>
       </c>
@@ -1069,14 +1072,14 @@
         <v>1</v>
       </c>
       <c r="L3" s="2">
-        <f>448.131556+145.327592</f>
-        <v>593.45914800000003</v>
+        <f>443.274104+132.5581</f>
+        <v>575.83220400000005</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.2">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B4" s="8" t="s">
         <v>64</v>
       </c>
@@ -1086,10 +1089,10 @@
       </c>
       <c r="L4" s="2">
         <f>+L2*L3</f>
-        <v>17429.895176760001</v>
-      </c>
-    </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.2">
+        <v>31670.771220000002</v>
+      </c>
+    </row>
+    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B5" s="8" t="s">
         <v>65</v>
       </c>
@@ -1098,14 +1101,14 @@
         <v>3</v>
       </c>
       <c r="L5" s="2">
-        <f>1764.644+178.017+352.099+629.9</f>
-        <v>2924.6600000000003</v>
+        <f>586.395+21.9+173.27+265.697</f>
+        <v>1047.2619999999999</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.2">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="6" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B6" s="8" t="s">
         <v>66</v>
       </c>
@@ -1123,13 +1126,14 @@
         <v>4</v>
       </c>
       <c r="L6" s="2">
-        <v>7602.0190000000002</v>
+        <f>8576.443+17.48</f>
+        <v>8593.9229999999989</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.2">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B7" s="8" t="s">
         <v>67</v>
       </c>
@@ -1145,10 +1149,10 @@
       </c>
       <c r="L7" s="2">
         <f>+L4-L5+L6</f>
-        <v>22107.254176760001</v>
-      </c>
-    </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.2">
+        <v>39217.432220000002</v>
+      </c>
+    </row>
+    <row r="8" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B8" s="8" t="s">
         <v>68</v>
       </c>
@@ -1157,7 +1161,7 @@
       </c>
       <c r="G8" s="9"/>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B9" s="8" t="s">
         <v>69</v>
       </c>
@@ -1172,7 +1176,7 @@
       </c>
       <c r="G9" s="9"/>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B10" s="8" t="s">
         <v>70</v>
       </c>
@@ -1181,7 +1185,7 @@
       </c>
       <c r="G10" s="9"/>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B11" s="8" t="s">
         <v>71</v>
       </c>
@@ -1196,7 +1200,7 @@
       </c>
       <c r="G11" s="9"/>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B12" s="8" t="s">
         <v>72</v>
       </c>
@@ -1214,7 +1218,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B13" s="8" t="s">
         <v>73</v>
       </c>
@@ -1229,7 +1233,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B14" s="8" t="s">
         <v>74</v>
       </c>
@@ -1244,7 +1248,7 @@
       </c>
       <c r="G14" s="9"/>
     </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B15" s="10"/>
       <c r="C15" s="11"/>
       <c r="D15" s="11"/>
@@ -1252,7 +1256,7 @@
       <c r="F15" s="11"/>
       <c r="G15" s="12"/>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>103</v>
       </c>
@@ -1266,20 +1270,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1713F4E8-A8CE-4B18-916E-E9E556347FDE}">
   <dimension ref="A1:AS77"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.5703125" customWidth="1"/>
-    <col min="3" max="14" width="9.140625" style="3"/>
-    <col min="45" max="45" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.54296875" customWidth="1"/>
+    <col min="3" max="14" width="9.1796875" style="3"/>
+    <col min="45" max="45" width="10.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:43" x14ac:dyDescent="0.25">
       <c r="C2" s="3" t="s">
         <v>9</v>
       </c>
@@ -1410,7 +1414,7 @@
         <v>2035</v>
       </c>
     </row>
-    <row r="3" spans="1:43" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:43" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
         <v>40</v>
       </c>
@@ -1438,7 +1442,7 @@
         <v>8931</v>
       </c>
     </row>
-    <row r="4" spans="1:43" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:43" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B4" s="2" t="s">
         <v>39</v>
       </c>
@@ -1519,7 +1523,7 @@
         <v>124.8376697489098</v>
       </c>
     </row>
-    <row r="5" spans="1:43" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
         <v>38</v>
       </c>
@@ -1539,7 +1543,7 @@
         <v>2028</v>
       </c>
     </row>
-    <row r="6" spans="1:43" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
         <v>41</v>
       </c>
@@ -1620,7 +1624,7 @@
         <v>189.93657081341681</v>
       </c>
     </row>
-    <row r="7" spans="1:43" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
         <v>42</v>
       </c>
@@ -1640,7 +1644,7 @@
         <v>5820</v>
       </c>
     </row>
-    <row r="8" spans="1:43" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B8" s="2" t="s">
         <v>43</v>
       </c>
@@ -1721,7 +1725,7 @@
         <v>79.560400426697726</v>
       </c>
     </row>
-    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
         <v>44</v>
       </c>
@@ -1735,7 +1739,7 @@
         <v>4817</v>
       </c>
     </row>
-    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.25">
       <c r="B10" s="2" t="s">
         <v>45</v>
       </c>
@@ -1803,7 +1807,7 @@
         <v>6.3279438735140934</v>
       </c>
     </row>
-    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.25">
       <c r="B11" s="2" t="s">
         <v>46</v>
       </c>
@@ -1817,7 +1821,7 @@
         <v>2088</v>
       </c>
     </row>
-    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.25">
       <c r="B12" s="2" t="s">
         <v>47</v>
       </c>
@@ -1885,7 +1889,7 @@
         <v>9.6541900000000076E-9</v>
       </c>
     </row>
-    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.25">
       <c r="B13" s="2" t="s">
         <v>48</v>
       </c>
@@ -1952,7 +1956,7 @@
       </c>
       <c r="AQ13" s="2"/>
     </row>
-    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
         <v>62</v>
       </c>
@@ -2025,7 +2029,7 @@
       </c>
       <c r="AQ14" s="2"/>
     </row>
-    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.25">
       <c r="B15" s="2" t="s">
         <v>49</v>
       </c>
@@ -2098,7 +2102,7 @@
       </c>
       <c r="AQ15" s="2"/>
     </row>
-    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.25">
       <c r="B16" s="2" t="s">
         <v>50</v>
       </c>
@@ -2170,7 +2174,7 @@
         <v>121.69710325425274</v>
       </c>
     </row>
-    <row r="17" spans="2:45" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:45" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="s">
         <v>51</v>
       </c>
@@ -2238,7 +2242,7 @@
         <v>1.0392829361207996</v>
       </c>
     </row>
-    <row r="18" spans="2:45" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:45" x14ac:dyDescent="0.25">
       <c r="B18" s="2" t="s">
         <v>61</v>
       </c>
@@ -2306,7 +2310,7 @@
         <v>3.6085500000000029E-8</v>
       </c>
     </row>
-    <row r="19" spans="2:45" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:45" x14ac:dyDescent="0.25">
       <c r="B19" s="2" t="s">
         <v>60</v>
       </c>
@@ -2374,7 +2378,7 @@
         <v>2.8763424000000014E-8</v>
       </c>
     </row>
-    <row r="20" spans="2:45" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:45" x14ac:dyDescent="0.25">
       <c r="B20" s="2" t="s">
         <v>59</v>
       </c>
@@ -2446,7 +2450,7 @@
         <v>43.232535733082479</v>
       </c>
     </row>
-    <row r="21" spans="2:45" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:45" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>58</v>
       </c>
@@ -2509,7 +2513,7 @@
         <v>39.355488304196136</v>
       </c>
     </row>
-    <row r="22" spans="2:45" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:45" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>57</v>
       </c>
@@ -2572,7 +2576,7 @@
         <v>56.26348217170257</v>
       </c>
     </row>
-    <row r="23" spans="2:45" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:45" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>56</v>
       </c>
@@ -2635,7 +2639,7 @@
         <v>29.479094978288483</v>
       </c>
     </row>
-    <row r="24" spans="2:45" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:45" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>55</v>
       </c>
@@ -2698,7 +2702,7 @@
         <v>28.395990759325638</v>
       </c>
     </row>
-    <row r="25" spans="2:45" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:45" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>54</v>
       </c>
@@ -2768,7 +2772,7 @@
         <v>28732.681743132147</v>
       </c>
     </row>
-    <row r="26" spans="2:45" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:45" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>53</v>
       </c>
@@ -2838,7 +2842,7 @@
         <v>27003.974817446797</v>
       </c>
     </row>
-    <row r="27" spans="2:45" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:45" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>52</v>
       </c>
@@ -2908,7 +2912,7 @@
         <v>25425.443574130655</v>
       </c>
     </row>
-    <row r="28" spans="2:45" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:45" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>102</v>
       </c>
@@ -2980,7 +2984,7 @@
         <v>23981.425369581204</v>
       </c>
     </row>
-    <row r="29" spans="2:45" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:45" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
         <v>104</v>
       </c>
@@ -3000,7 +3004,7 @@
         <v>22658.103509842338</v>
       </c>
     </row>
-    <row r="30" spans="2:45" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:45" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>105</v>
       </c>
@@ -3021,7 +3025,7 @@
         <v>21443.26837156502</v>
       </c>
     </row>
-    <row r="31" spans="2:45" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:45" x14ac:dyDescent="0.25">
       <c r="AR31" s="16">
         <f t="shared" si="32"/>
         <v>7.0000000000000007E-2</v>
@@ -3031,7 +3035,7 @@
         <v>20326.111905131995</v>
       </c>
     </row>
-    <row r="32" spans="2:45" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:45" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B32" s="2" t="s">
         <v>20</v>
       </c>
@@ -3069,7 +3073,7 @@
         <v>19297.050536907314</v>
       </c>
     </row>
-    <row r="33" spans="2:45" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:45" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B33" s="2" t="s">
         <v>21</v>
       </c>
@@ -3107,7 +3111,7 @@
         <v>18347.572275962833</v>
       </c>
     </row>
-    <row r="34" spans="2:45" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:45" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B34" s="2" t="s">
         <v>22</v>
       </c>
@@ -3151,7 +3155,7 @@
         <v>17470.10448759262</v>
       </c>
     </row>
-    <row r="35" spans="2:45" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:45" s="5" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="B35" s="5" t="s">
         <v>8</v>
       </c>
@@ -3202,7 +3206,7 @@
         <v>16657.899344433183</v>
       </c>
     </row>
-    <row r="36" spans="2:45" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:45" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B36" s="2" t="s">
         <v>23</v>
       </c>
@@ -3238,7 +3242,7 @@
         <v>904.24400000000003</v>
       </c>
     </row>
-    <row r="37" spans="2:45" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:45" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B37" s="2" t="s">
         <v>24</v>
       </c>
@@ -3274,7 +3278,7 @@
         <v>177.10599999999999</v>
       </c>
     </row>
-    <row r="38" spans="2:45" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:45" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B38" s="2" t="s">
         <v>25</v>
       </c>
@@ -3310,7 +3314,7 @@
         <v>227.303</v>
       </c>
     </row>
-    <row r="39" spans="2:45" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:45" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B39" s="2" t="s">
         <v>29</v>
       </c>
@@ -3353,7 +3357,7 @@
         <v>1308.6529999999998</v>
       </c>
     </row>
-    <row r="40" spans="2:45" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:45" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B40" s="2" t="s">
         <v>28</v>
       </c>
@@ -3396,7 +3400,7 @@
         <v>928.56200000000035</v>
       </c>
     </row>
-    <row r="41" spans="2:45" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:45" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B41" s="2" t="s">
         <v>26</v>
       </c>
@@ -3435,7 +3439,7 @@
         <v>-187.96100000000001</v>
       </c>
     </row>
-    <row r="42" spans="2:45" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:45" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B42" s="2" t="s">
         <v>27</v>
       </c>
@@ -3458,7 +3462,7 @@
       </c>
       <c r="N42" s="4"/>
       <c r="P42" s="2">
-        <f t="shared" ref="P42:S42" si="33">+P40+P41</f>
+        <f t="shared" ref="P42" si="33">+P40+P41</f>
         <v>201.89099999999996</v>
       </c>
       <c r="T42" s="2">
@@ -3478,7 +3482,7 @@
         <v>740.60100000000034</v>
       </c>
     </row>
-    <row r="43" spans="2:45" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:45" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B43" s="2" t="s">
         <v>30</v>
       </c>
@@ -3511,7 +3515,7 @@
         <v>621.47299999999996</v>
       </c>
     </row>
-    <row r="44" spans="2:45" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:45" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B44" s="2" t="s">
         <v>31</v>
       </c>
@@ -3534,7 +3538,7 @@
       </c>
       <c r="N44" s="4"/>
       <c r="P44" s="2">
-        <f t="shared" ref="P44:S44" si="34">+P42-P43</f>
+        <f t="shared" ref="P44" si="34">+P42-P43</f>
         <v>201.89099999999996</v>
       </c>
       <c r="T44" s="2">
@@ -3554,7 +3558,7 @@
         <v>119.12800000000038</v>
       </c>
     </row>
-    <row r="45" spans="2:45" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:45" x14ac:dyDescent="0.25">
       <c r="B45" s="2" t="s">
         <v>32</v>
       </c>
@@ -3583,7 +3587,7 @@
         <v>0.19618460403409677</v>
       </c>
     </row>
-    <row r="46" spans="2:45" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:45" x14ac:dyDescent="0.25">
       <c r="B46" s="2" t="s">
         <v>1</v>
       </c>
@@ -3611,7 +3615,7 @@
         <v>607.22400000000005</v>
       </c>
     </row>
-    <row r="48" spans="2:45" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:45" x14ac:dyDescent="0.25">
       <c r="B48" s="2" t="s">
         <v>106</v>
       </c>
@@ -3624,7 +3628,7 @@
         <v>3231.4569999999999</v>
       </c>
     </row>
-    <row r="49" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B49" s="2" t="s">
         <v>107</v>
       </c>
@@ -3635,7 +3639,7 @@
         <v>441.96300000000002</v>
       </c>
     </row>
-    <row r="50" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="50" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B50" s="2" t="s">
         <v>108</v>
       </c>
@@ -3648,7 +3652,7 @@
         <v>2789.4939999999997</v>
       </c>
     </row>
-    <row r="51" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B51" s="2" t="s">
         <v>109</v>
       </c>
@@ -3659,7 +3663,7 @@
         <v>222.96899999999999</v>
       </c>
     </row>
-    <row r="52" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B52" s="2" t="s">
         <v>110</v>
       </c>
@@ -3672,7 +3676,7 @@
         <v>2566.5249999999996</v>
       </c>
     </row>
-    <row r="53" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="53" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B53" s="2" t="s">
         <v>111</v>
       </c>
@@ -3685,7 +3689,7 @@
         <v>177.10599999999999</v>
       </c>
     </row>
-    <row r="54" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B54" s="2" t="s">
         <v>112</v>
       </c>
@@ -3696,7 +3700,7 @@
         <v>145.15700000000001</v>
       </c>
     </row>
-    <row r="55" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="55" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B55" s="2" t="s">
         <v>113</v>
       </c>
@@ -3709,7 +3713,7 @@
         <v>8.8370000000000015</v>
       </c>
     </row>
-    <row r="56" spans="2:29" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="2:29" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B56" s="2" t="s">
         <v>33</v>
       </c>
@@ -3740,7 +3744,7 @@
         <v>2235.4249999999997</v>
       </c>
     </row>
-    <row r="57" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="57" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B57" s="2" t="s">
         <v>114</v>
       </c>
@@ -3751,7 +3755,7 @@
         <v>607.22400000000005</v>
       </c>
     </row>
-    <row r="58" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="58" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B58" s="2" t="s">
         <v>115</v>
       </c>
@@ -3764,7 +3768,7 @@
         <v>3.6813844643821714</v>
       </c>
     </row>
-    <row r="60" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="60" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B60" s="2" t="s">
         <v>3</v>
       </c>
@@ -3773,7 +3777,7 @@
         <v>2472.2950000000001</v>
       </c>
     </row>
-    <row r="61" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B61" s="2" t="s">
         <v>116</v>
       </c>
@@ -3782,7 +3786,7 @@
         <v>14184.424999999999</v>
       </c>
     </row>
-    <row r="62" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="62" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B62" s="2" t="s">
         <v>117</v>
       </c>
@@ -3791,7 +3795,7 @@
         <v>36.596999999999994</v>
       </c>
     </row>
-    <row r="63" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="63" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B63" s="2" t="s">
         <v>118</v>
       </c>
@@ -3800,7 +3804,7 @@
         <v>120.149</v>
       </c>
     </row>
-    <row r="64" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="64" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B64" s="2" t="s">
         <v>119</v>
       </c>
@@ -3809,7 +3813,7 @@
         <v>16813.466000000004</v>
       </c>
     </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B66" s="2" t="s">
         <v>120</v>
       </c>
@@ -3818,7 +3822,7 @@
         <v>94.802999999999997</v>
       </c>
     </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B67" s="2" t="s">
         <v>121</v>
       </c>
@@ -3826,7 +3830,7 @@
         <v>7.9059999999999997</v>
       </c>
     </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B68" s="2" t="s">
         <v>112</v>
       </c>
@@ -3834,7 +3838,7 @@
         <v>54.161999999999999</v>
       </c>
     </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B69" s="2" t="s">
         <v>4</v>
       </c>
@@ -3843,7 +3847,7 @@
         <v>7116.3220000000001</v>
       </c>
     </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B70" s="2" t="s">
         <v>122</v>
       </c>
@@ -3852,7 +3856,7 @@
         <v>14.9</v>
       </c>
     </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B71" s="2" t="s">
         <v>123</v>
       </c>
@@ -3861,7 +3865,7 @@
         <v>7288.0929999999998</v>
       </c>
     </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B74" s="2" t="s">
         <v>124</v>
       </c>
@@ -3884,7 +3888,7 @@
         <v>2143.98</v>
       </c>
     </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B75" s="2" t="s">
         <v>125</v>
       </c>
@@ -3898,7 +3902,7 @@
         <v>1741.64</v>
       </c>
     </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B76" s="2" t="s">
         <v>126</v>
       </c>
@@ -3912,7 +3916,7 @@
         <v>441.96300000000002</v>
       </c>
     </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B77" s="2" t="s">
         <v>127</v>
       </c>
